--- a/Docs/Cases.xlsx
+++ b/Docs/Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engar\IdeaProjects\aqa_diplom\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F374645-7F35-40A0-980B-A353CF586E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CA8E0C-0D7D-4CF0-AAAF-F7561D5A6ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="361">
   <si>
     <t>ID</t>
   </si>
@@ -1189,10 +1189,6 @@
     <t>На всех страницах приложения текст отображен лаконично без выходов за границы</t>
   </si>
   <si>
-    <t>Статус
-(☑/☐/✗)</t>
-  </si>
-  <si>
     <t>Полная адаптация приложения к горизонтальной ориентации
 (позитивный)</t>
   </si>
@@ -1202,6 +1198,14 @@
   </si>
   <si>
     <t>✗</t>
+  </si>
+  <si>
+    <t>Статус ручного тестирования
+(☑/☐/✗)</t>
+  </si>
+  <si>
+    <t>Статус автоматизированного тестирования
+(☑/☐/✗)</t>
   </si>
 </sst>
 </file>
@@ -1496,7 +1500,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1510,29 +1514,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1543,40 +1529,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1600,25 +1556,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1630,12 +1568,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1645,19 +1577,88 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1667,6 +1668,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1966,7 +1979,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:I215"/>
+  <dimension ref="A1:J215"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -1976,12 +1989,13 @@
     <col min="5" max="5" width="30.42578125" customWidth="1"/>
     <col min="6" max="6" width="27.5703125" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="32.42578125" customWidth="1"/>
-    <col min="10" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2004,20 +2018,23 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>356</v>
+        <v>168</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="24" t="s">
         <v>80</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -2029,327 +2046,357 @@
       <c r="F2" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" s="8"/>
-    </row>
-    <row r="3" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="49" t="s">
+      <c r="B3" s="37"/>
+      <c r="C3" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="7" t="s">
         <v>138</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="45" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="22" t="s">
+      <c r="H4" s="27"/>
+      <c r="I4" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="34"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-    </row>
-    <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="22" t="s">
+      <c r="G5" s="43"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+    </row>
+    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="35"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-    </row>
-    <row r="7" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="G6" s="44"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+    </row>
+    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="51" t="s">
+      <c r="B7" s="37"/>
+      <c r="C7" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="36" t="s">
         <v>177</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="22" t="s">
+      <c r="H7" s="27"/>
+      <c r="I7" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="34"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="22" t="s">
+      <c r="G8" s="41"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+    </row>
+    <row r="9" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="35"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-    </row>
-    <row r="10" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="G9" s="40"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+    </row>
+    <row r="10" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="51" t="s">
+      <c r="B10" s="37"/>
+      <c r="C10" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="22" t="s">
+      <c r="H10" s="27"/>
+      <c r="I10" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="35"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="G11" s="40"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="51" t="s">
+      <c r="B12" s="37"/>
+      <c r="C12" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="22" t="s">
+      <c r="H12" s="27"/>
+      <c r="I12" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="35"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-    </row>
-    <row r="14" spans="1:9" ht="51" x14ac:dyDescent="0.25">
+      <c r="G13" s="40"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+    </row>
+    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="54" t="s">
+      <c r="B14" s="38"/>
+      <c r="C14" s="26" t="s">
         <v>129</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="22" t="s">
         <v>83</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="7" t="s">
         <v>150</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="45" t="s">
+      <c r="B16" s="37"/>
+      <c r="C16" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="12" t="s">
         <v>154</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H16" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="14" t="s">
+      <c r="H16" s="27"/>
+      <c r="I16" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="27"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="35"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-    </row>
-    <row r="18" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="40"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+    </row>
+    <row r="18" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="47" t="s">
+      <c r="B18" s="37"/>
+      <c r="C18" s="23" t="s">
         <v>86</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -2361,22 +2408,23 @@
       <c r="F18" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="I18" s="8" t="s">
+      <c r="H18" s="5" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="I18" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="44" t="s">
+      <c r="B19" s="38"/>
+      <c r="C19" s="22" t="s">
         <v>85</v>
       </c>
       <c r="D19" s="4" t="s">
@@ -2388,25 +2436,28 @@
       <c r="F19" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="H19" s="5"/>
+      <c r="I19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="36" t="s">
         <v>184</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -2415,38 +2466,42 @@
       <c r="F20" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H20" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" s="19"/>
-    </row>
-    <row r="21" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="7"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J20" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="35"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="38"/>
       <c r="E21" s="3" t="s">
         <v>160</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-    </row>
-    <row r="22" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="G21" s="40"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+    </row>
+    <row r="22" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="39" t="s">
+      <c r="B22" s="37"/>
+      <c r="C22" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="36" t="s">
         <v>179</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -2455,38 +2510,40 @@
       <c r="F22" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H22" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I22" s="19"/>
-    </row>
-    <row r="23" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="7"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J22" s="27"/>
+    </row>
+    <row r="23" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="35"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="38"/>
       <c r="E23" s="3" t="s">
         <v>160</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-    </row>
-    <row r="24" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="G23" s="40"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+    </row>
+    <row r="24" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="39" t="s">
+      <c r="B24" s="37"/>
+      <c r="C24" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="36" t="s">
         <v>178</v>
       </c>
       <c r="E24" s="4" t="s">
@@ -2495,38 +2552,40 @@
       <c r="F24" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H24" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I24" s="19"/>
-    </row>
-    <row r="25" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="7"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J24" s="27"/>
+    </row>
+    <row r="25" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="35"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="3" t="s">
         <v>170</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-    </row>
-    <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="G25" s="40"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="39" t="s">
+      <c r="B26" s="37"/>
+      <c r="C26" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="36" t="s">
         <v>179</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -2535,38 +2594,40 @@
       <c r="F26" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H26" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I26" s="19"/>
-    </row>
-    <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="7"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="35"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="38"/>
       <c r="E27" s="3" t="s">
         <v>170</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G27" s="18"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-    </row>
-    <row r="28" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="G27" s="40"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="39" t="s">
+      <c r="B28" s="37"/>
+      <c r="C28" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="36" t="s">
         <v>184</v>
       </c>
       <c r="E28" s="4" t="s">
@@ -2575,38 +2636,42 @@
       <c r="F28" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H28" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I28" s="19"/>
-    </row>
-    <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="7"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J28" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="35"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="38"/>
       <c r="E29" s="3" t="s">
         <v>167</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G29" s="18"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-    </row>
-    <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+      <c r="G29" s="40"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+    </row>
+    <row r="30" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="39" t="s">
+      <c r="B30" s="37"/>
+      <c r="C30" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="36" t="s">
         <v>178</v>
       </c>
       <c r="E30" s="4" t="s">
@@ -2615,40 +2680,42 @@
       <c r="F30" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H30" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="I30" s="19" t="s">
+      <c r="H30" s="27" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="7"/>
+      <c r="I30" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="J30" s="27"/>
+    </row>
+    <row r="31" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="38"/>
       <c r="E31" s="3" t="s">
         <v>167</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G31" s="18"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-    </row>
-    <row r="32" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="G31" s="40"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+    </row>
+    <row r="32" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="39" t="s">
+      <c r="B32" s="37"/>
+      <c r="C32" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="36" t="s">
         <v>180</v>
       </c>
       <c r="E32" s="4" t="s">
@@ -2657,38 +2724,40 @@
       <c r="F32" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H32" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I32" s="19"/>
-    </row>
-    <row r="33" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="7"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J32" s="27"/>
+    </row>
+    <row r="33" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="35"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="38"/>
       <c r="E33" s="3" t="s">
         <v>167</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G33" s="18"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-    </row>
-    <row r="34" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="G33" s="40"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+    </row>
+    <row r="34" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="43" t="s">
+      <c r="B34" s="37"/>
+      <c r="C34" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="7" t="s">
         <v>181</v>
       </c>
       <c r="E34" s="4" t="s">
@@ -2697,23 +2766,26 @@
       <c r="F34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="H34" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="I34" s="30"/>
-    </row>
-    <row r="35" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="H34" s="14"/>
+      <c r="I34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="43" t="s">
+      <c r="B35" s="37"/>
+      <c r="C35" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="7" t="s">
         <v>182</v>
       </c>
       <c r="E35" s="4" t="s">
@@ -2722,23 +2794,24 @@
       <c r="F35" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G35" s="29" t="s">
+      <c r="G35" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="I35" s="30"/>
-    </row>
-    <row r="36" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="H35" s="14"/>
+      <c r="I35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="39" t="s">
+      <c r="B36" s="37"/>
+      <c r="C36" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="36" t="s">
         <v>181</v>
       </c>
       <c r="E36" s="4" t="s">
@@ -2747,38 +2820,42 @@
       <c r="F36" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H36" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I36" s="19"/>
-    </row>
-    <row r="37" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="7"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J36" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="35"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="38"/>
       <c r="E37" s="4" t="s">
         <v>174</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="G37" s="18"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-    </row>
-    <row r="38" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="G37" s="40"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+    </row>
+    <row r="38" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="39" t="s">
+      <c r="B38" s="37"/>
+      <c r="C38" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="36" t="s">
         <v>182</v>
       </c>
       <c r="E38" s="4" t="s">
@@ -2787,35 +2864,39 @@
       <c r="F38" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H38" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I38" s="19"/>
-    </row>
-    <row r="39" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="7"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J38" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A39" s="35"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="38"/>
       <c r="E39" s="4" t="s">
         <v>174</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="G39" s="18"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-    </row>
-    <row r="40" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="40"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+    </row>
+    <row r="40" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="42" t="s">
+      <c r="B40" s="38"/>
+      <c r="C40" s="20" t="s">
         <v>96</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2827,25 +2908,28 @@
       <c r="F40" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H40" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I40" s="8"/>
-    </row>
-    <row r="41" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+      <c r="H40" s="5"/>
+      <c r="I40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E41" s="4" t="s">
@@ -2854,175 +2938,188 @@
       <c r="F41" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H41" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I41" s="19" t="s">
+      <c r="H41" s="27" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A42" s="11"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="6"/>
+      <c r="I41" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J41" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A42" s="34"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="37"/>
       <c r="E42" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G42" s="17"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-    </row>
-    <row r="43" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A43" s="11"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="6"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+    </row>
+    <row r="43" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="37"/>
       <c r="E43" s="4" t="s">
         <v>189</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="G43" s="17"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-    </row>
-    <row r="44" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="11"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="6"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+    </row>
+    <row r="44" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="34"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="37"/>
       <c r="E44" s="4" t="s">
         <v>187</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G44" s="17"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-    </row>
-    <row r="45" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="11"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="6"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
+    </row>
+    <row r="45" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A45" s="34"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="37"/>
       <c r="E45" s="4" t="s">
         <v>193</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G45" s="17"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-    </row>
-    <row r="46" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A46" s="11"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="6"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+    </row>
+    <row r="46" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A46" s="34"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="37"/>
       <c r="E46" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="G46" s="17"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="11"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="6"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="34"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="37"/>
       <c r="E47" s="4" t="s">
         <v>196</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G47" s="17"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="11"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="6"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="34"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="37"/>
       <c r="E48" s="4" t="s">
         <v>226</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="G48" s="17"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-    </row>
-    <row r="49" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="11"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="6"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+    </row>
+    <row r="49" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="34"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="37"/>
       <c r="E49" s="4" t="s">
         <v>220</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="G49" s="17"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-    </row>
-    <row r="50" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="11"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="6"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+    </row>
+    <row r="50" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="34"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="37"/>
       <c r="E50" s="4" t="s">
         <v>200</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G50" s="17"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-    </row>
-    <row r="51" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="11"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="6"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+    </row>
+    <row r="51" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="34"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="37"/>
       <c r="E51" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="G51" s="17"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-    </row>
-    <row r="52" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+      <c r="G51" s="41"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+    </row>
+    <row r="52" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="39" t="s">
+      <c r="B52" s="37"/>
+      <c r="C52" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -3031,188 +3128,200 @@
       <c r="F52" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G52" s="16" t="s">
+      <c r="G52" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H52" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I52" s="19"/>
-    </row>
-    <row r="53" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="6"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J52" s="27"/>
+    </row>
+    <row r="53" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="34"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="37"/>
       <c r="E53" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G53" s="17"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-    </row>
-    <row r="54" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A54" s="11"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="6"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="28"/>
+    </row>
+    <row r="54" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A54" s="34"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="37"/>
       <c r="E54" s="4" t="s">
         <v>189</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="G54" s="17"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-    </row>
-    <row r="55" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="6"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+    </row>
+    <row r="55" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="34"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="37"/>
       <c r="E55" s="4" t="s">
         <v>187</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G55" s="17"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-    </row>
-    <row r="56" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="11"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="6"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+    </row>
+    <row r="56" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A56" s="34"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="37"/>
       <c r="E56" s="4" t="s">
         <v>193</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G56" s="17"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-    </row>
-    <row r="57" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A57" s="11"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="6"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+    </row>
+    <row r="57" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A57" s="34"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="37"/>
       <c r="E57" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="G57" s="17"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="11"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="6"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="34"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="37"/>
       <c r="E58" s="4" t="s">
         <v>196</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G58" s="17"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="6"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="34"/>
+      <c r="B59" s="37"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="37"/>
       <c r="E59" s="4" t="s">
         <v>226</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="G59" s="17"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-    </row>
-    <row r="60" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="6"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+    </row>
+    <row r="60" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A60" s="34"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="37"/>
       <c r="E60" s="4" t="s">
         <v>220</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="G60" s="17"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-    </row>
-    <row r="61" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="6"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+    </row>
+    <row r="61" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="37"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="37"/>
       <c r="E61" s="4" t="s">
         <v>200</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G61" s="17"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-    </row>
-    <row r="62" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="40"/>
-      <c r="D62" s="6"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+    </row>
+    <row r="62" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A62" s="34"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="37"/>
       <c r="E62" s="4" t="s">
         <v>204</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="G62" s="17"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-    </row>
-    <row r="63" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="7"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="28"/>
+    </row>
+    <row r="63" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="35"/>
+      <c r="B63" s="37"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="38"/>
       <c r="E63" s="4" t="s">
         <v>207</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G63" s="18"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-    </row>
-    <row r="64" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
+      <c r="G63" s="40"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="29"/>
+    </row>
+    <row r="64" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="55" t="s">
+      <c r="B64" s="37"/>
+      <c r="C64" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -3221,53 +3330,58 @@
       <c r="F64" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G64" s="16" t="s">
+      <c r="G64" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H64" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I64" s="19"/>
-    </row>
-    <row r="65" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="56"/>
-      <c r="D65" s="6"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J64" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A65" s="34"/>
+      <c r="B65" s="37"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="37"/>
       <c r="E65" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G65" s="17"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-    </row>
-    <row r="66" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="12"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="57"/>
-      <c r="D66" s="7"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="28"/>
+      <c r="J65" s="28"/>
+    </row>
+    <row r="66" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="35"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="56"/>
+      <c r="D66" s="38"/>
       <c r="E66" s="4" t="s">
         <v>208</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G66" s="18"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="21"/>
-    </row>
-    <row r="67" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="10" t="s">
+      <c r="G66" s="40"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="29"/>
+    </row>
+    <row r="67" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="55" t="s">
+      <c r="B67" s="37"/>
+      <c r="C67" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D67" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E67" s="4" t="s">
@@ -3276,158 +3390,170 @@
       <c r="F67" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G67" s="16" t="s">
+      <c r="G67" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H67" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I67" s="19"/>
-    </row>
-    <row r="68" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="11"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="56"/>
-      <c r="D68" s="6"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J67" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A68" s="34"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="55"/>
+      <c r="D68" s="37"/>
       <c r="E68" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G68" s="17"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-    </row>
-    <row r="69" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="11"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="56"/>
-      <c r="D69" s="6"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="28"/>
+    </row>
+    <row r="69" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="34"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="55"/>
+      <c r="D69" s="37"/>
       <c r="E69" s="4" t="s">
         <v>213</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="G69" s="17"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-    </row>
-    <row r="70" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="11"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="56"/>
-      <c r="D70" s="6"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+      <c r="J69" s="28"/>
+    </row>
+    <row r="70" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="34"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="55"/>
+      <c r="D70" s="37"/>
       <c r="E70" s="4" t="s">
         <v>187</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="G70" s="17"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-    </row>
-    <row r="71" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="11"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="56"/>
-      <c r="D71" s="6"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+    </row>
+    <row r="71" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A71" s="34"/>
+      <c r="B71" s="37"/>
+      <c r="C71" s="55"/>
+      <c r="D71" s="37"/>
       <c r="E71" s="4" t="s">
         <v>193</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G71" s="17"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-    </row>
-    <row r="72" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A72" s="11"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="56"/>
-      <c r="D72" s="6"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="28"/>
+      <c r="I71" s="28"/>
+      <c r="J71" s="28"/>
+    </row>
+    <row r="72" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A72" s="34"/>
+      <c r="B72" s="37"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="37"/>
       <c r="E72" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="G72" s="17"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="11"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="56"/>
-      <c r="D73" s="6"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="28"/>
+      <c r="J72" s="28"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="37"/>
       <c r="E73" s="4" t="s">
         <v>196</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G73" s="17"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="11"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="56"/>
-      <c r="D74" s="6"/>
+      <c r="G73" s="41"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="28"/>
+      <c r="J73" s="28"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="34"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="55"/>
+      <c r="D74" s="37"/>
       <c r="E74" s="4" t="s">
         <v>226</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="G74" s="17"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-    </row>
-    <row r="75" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="11"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="56"/>
-      <c r="D75" s="6"/>
+      <c r="G74" s="41"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="28"/>
+      <c r="J74" s="28"/>
+    </row>
+    <row r="75" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="34"/>
+      <c r="B75" s="37"/>
+      <c r="C75" s="55"/>
+      <c r="D75" s="37"/>
       <c r="E75" s="4" t="s">
         <v>211</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G75" s="17"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
-    </row>
-    <row r="76" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="12"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="57"/>
-      <c r="D76" s="7"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="28"/>
+      <c r="J75" s="28"/>
+    </row>
+    <row r="76" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="35"/>
+      <c r="B76" s="37"/>
+      <c r="C76" s="56"/>
+      <c r="D76" s="38"/>
       <c r="E76" s="4" t="s">
         <v>212</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G76" s="18"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-    </row>
-    <row r="77" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="10" t="s">
+      <c r="G76" s="40"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+    </row>
+    <row r="77" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="55" t="s">
+      <c r="B77" s="37"/>
+      <c r="C77" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E77" s="4" t="s">
@@ -3436,128 +3562,138 @@
       <c r="F77" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G77" s="16" t="s">
+      <c r="G77" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H77" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I77" s="19"/>
-    </row>
-    <row r="78" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A78" s="11"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="56"/>
-      <c r="D78" s="6"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J77" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="34"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="55"/>
+      <c r="D78" s="37"/>
       <c r="E78" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G78" s="17"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
-    </row>
-    <row r="79" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="56"/>
-      <c r="D79" s="6"/>
+      <c r="G78" s="41"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="28"/>
+    </row>
+    <row r="79" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A79" s="34"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="55"/>
+      <c r="D79" s="37"/>
       <c r="E79" s="4" t="s">
         <v>214</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="G79" s="17"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
-    </row>
-    <row r="80" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="11"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="56"/>
-      <c r="D80" s="6"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="28"/>
+      <c r="I79" s="28"/>
+      <c r="J79" s="28"/>
+    </row>
+    <row r="80" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="34"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="37"/>
       <c r="E80" s="4" t="s">
         <v>187</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="G80" s="17"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="11"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="56"/>
-      <c r="D81" s="6"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="28"/>
+      <c r="I80" s="28"/>
+      <c r="J80" s="28"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="34"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="55"/>
+      <c r="D81" s="37"/>
       <c r="E81" s="4" t="s">
         <v>351</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G81" s="17"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="11"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="56"/>
-      <c r="D82" s="6"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="28"/>
+      <c r="J81" s="28"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="34"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="55"/>
+      <c r="D82" s="37"/>
       <c r="E82" s="4" t="s">
         <v>352</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="G82" s="17"/>
-      <c r="H82" s="20"/>
-      <c r="I82" s="20"/>
-    </row>
-    <row r="83" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="11"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="56"/>
-      <c r="D83" s="6"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="28"/>
+      <c r="J82" s="28"/>
+    </row>
+    <row r="83" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A83" s="34"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="55"/>
+      <c r="D83" s="37"/>
       <c r="E83" s="4" t="s">
         <v>224</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G83" s="17"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-    </row>
-    <row r="84" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="12"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="57"/>
-      <c r="D84" s="7"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="28"/>
+      <c r="J83" s="28"/>
+    </row>
+    <row r="84" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="35"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="38"/>
       <c r="E84" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G84" s="18"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="21"/>
-    </row>
-    <row r="85" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A85" s="10" t="s">
+      <c r="G84" s="40"/>
+      <c r="H84" s="29"/>
+      <c r="I84" s="29"/>
+      <c r="J84" s="29"/>
+    </row>
+    <row r="85" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B85" s="6"/>
-      <c r="C85" s="39" t="s">
+      <c r="B85" s="37"/>
+      <c r="C85" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="D85" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E85" s="4" t="s">
@@ -3566,68 +3702,72 @@
       <c r="F85" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G85" s="16" t="s">
+      <c r="G85" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H85" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I85" s="19"/>
-    </row>
-    <row r="86" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A86" s="11"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="40"/>
-      <c r="D86" s="6"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J85" s="27"/>
+    </row>
+    <row r="86" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A86" s="34"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="37"/>
       <c r="E86" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G86" s="17"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-    </row>
-    <row r="87" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A87" s="11"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="40"/>
-      <c r="D87" s="6"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="28"/>
+      <c r="I86" s="28"/>
+      <c r="J86" s="28"/>
+    </row>
+    <row r="87" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="34"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="37"/>
       <c r="E87" s="4" t="s">
         <v>216</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G87" s="17"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
-    </row>
-    <row r="88" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A88" s="12"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="41"/>
-      <c r="D88" s="7"/>
+      <c r="G87" s="41"/>
+      <c r="H87" s="28"/>
+      <c r="I87" s="28"/>
+      <c r="J87" s="28"/>
+    </row>
+    <row r="88" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="35"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="38"/>
       <c r="E88" s="4" t="s">
         <v>223</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="G88" s="18"/>
-      <c r="H88" s="21"/>
-      <c r="I88" s="21"/>
-    </row>
-    <row r="89" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A89" s="10" t="s">
+      <c r="G88" s="40"/>
+      <c r="H88" s="29"/>
+      <c r="I88" s="29"/>
+      <c r="J88" s="29"/>
+    </row>
+    <row r="89" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A89" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="39" t="s">
+      <c r="B89" s="37"/>
+      <c r="C89" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D89" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E89" s="4" t="s">
@@ -3636,68 +3776,72 @@
       <c r="F89" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G89" s="16" t="s">
+      <c r="G89" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H89" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I89" s="19"/>
-    </row>
-    <row r="90" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A90" s="11"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="40"/>
-      <c r="D90" s="6"/>
+      <c r="H89" s="27"/>
+      <c r="I89" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J89" s="27"/>
+    </row>
+    <row r="90" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="34"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="37"/>
       <c r="E90" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G90" s="17"/>
-      <c r="H90" s="20"/>
-      <c r="I90" s="20"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="11"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="40"/>
-      <c r="D91" s="6"/>
+      <c r="G90" s="41"/>
+      <c r="H90" s="28"/>
+      <c r="I90" s="28"/>
+      <c r="J90" s="28"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="34"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="57"/>
+      <c r="D91" s="37"/>
       <c r="E91" s="4" t="s">
         <v>218</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G91" s="17"/>
-      <c r="H91" s="20"/>
-      <c r="I91" s="20"/>
-    </row>
-    <row r="92" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A92" s="12"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="41"/>
-      <c r="D92" s="7"/>
+      <c r="G91" s="41"/>
+      <c r="H91" s="28"/>
+      <c r="I91" s="28"/>
+      <c r="J91" s="28"/>
+    </row>
+    <row r="92" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A92" s="35"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="38"/>
       <c r="E92" s="4" t="s">
         <v>222</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="G92" s="18"/>
-      <c r="H92" s="21"/>
-      <c r="I92" s="21"/>
-    </row>
-    <row r="93" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A93" s="10" t="s">
+      <c r="G92" s="40"/>
+      <c r="H92" s="29"/>
+      <c r="I92" s="29"/>
+      <c r="J92" s="29"/>
+    </row>
+    <row r="93" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="B93" s="6"/>
-      <c r="C93" s="55" t="s">
+      <c r="B93" s="37"/>
+      <c r="C93" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="D93" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E93" s="4" t="s">
@@ -3706,130 +3850,140 @@
       <c r="F93" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G93" s="16" t="s">
+      <c r="G93" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H93" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I93" s="19"/>
-    </row>
-    <row r="94" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A94" s="11"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="56"/>
-      <c r="D94" s="6"/>
+      <c r="H93" s="27"/>
+      <c r="I93" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J93" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A94" s="34"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="37"/>
       <c r="E94" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G94" s="17"/>
-      <c r="H94" s="20"/>
-      <c r="I94" s="20"/>
-    </row>
-    <row r="95" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A95" s="11"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="56"/>
-      <c r="D95" s="6"/>
+      <c r="G94" s="41"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="28"/>
+      <c r="J94" s="28"/>
+    </row>
+    <row r="95" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A95" s="34"/>
+      <c r="B95" s="37"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="37"/>
       <c r="E95" s="4" t="s">
         <v>189</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="G95" s="17"/>
-      <c r="H95" s="20"/>
-      <c r="I95" s="20"/>
-    </row>
-    <row r="96" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="11"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="56"/>
-      <c r="D96" s="6"/>
+      <c r="G95" s="41"/>
+      <c r="H95" s="28"/>
+      <c r="I95" s="28"/>
+      <c r="J95" s="28"/>
+    </row>
+    <row r="96" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="34"/>
+      <c r="B96" s="37"/>
+      <c r="C96" s="55"/>
+      <c r="D96" s="37"/>
       <c r="E96" s="4" t="s">
         <v>187</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G96" s="17"/>
-      <c r="H96" s="20"/>
-      <c r="I96" s="20"/>
-    </row>
-    <row r="97" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A97" s="11"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="6"/>
+      <c r="G96" s="41"/>
+      <c r="H96" s="28"/>
+      <c r="I96" s="28"/>
+      <c r="J96" s="28"/>
+    </row>
+    <row r="97" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A97" s="34"/>
+      <c r="B97" s="37"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="37"/>
       <c r="E97" s="4" t="s">
         <v>193</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G97" s="17"/>
-      <c r="H97" s="20"/>
-      <c r="I97" s="20"/>
-    </row>
-    <row r="98" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A98" s="11"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="56"/>
-      <c r="D98" s="6"/>
+      <c r="G97" s="41"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="28"/>
+      <c r="J97" s="28"/>
+    </row>
+    <row r="98" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A98" s="34"/>
+      <c r="B98" s="37"/>
+      <c r="C98" s="55"/>
+      <c r="D98" s="37"/>
       <c r="E98" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="G98" s="17"/>
-      <c r="H98" s="20"/>
-      <c r="I98" s="20"/>
-    </row>
-    <row r="99" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="11"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="56"/>
-      <c r="D99" s="6"/>
+      <c r="G98" s="41"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="28"/>
+      <c r="J98" s="28"/>
+    </row>
+    <row r="99" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="34"/>
+      <c r="B99" s="37"/>
+      <c r="C99" s="55"/>
+      <c r="D99" s="37"/>
       <c r="E99" s="4" t="s">
         <v>224</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G99" s="17"/>
-      <c r="H99" s="20"/>
-      <c r="I99" s="20"/>
-    </row>
-    <row r="100" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="57"/>
-      <c r="D100" s="7"/>
+      <c r="G99" s="41"/>
+      <c r="H99" s="28"/>
+      <c r="I99" s="28"/>
+      <c r="J99" s="28"/>
+    </row>
+    <row r="100" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A100" s="35"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="56"/>
+      <c r="D100" s="38"/>
       <c r="E100" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G100" s="18"/>
-      <c r="H100" s="21"/>
-      <c r="I100" s="21"/>
-    </row>
-    <row r="101" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="10" t="s">
+      <c r="G100" s="40"/>
+      <c r="H100" s="29"/>
+      <c r="I100" s="29"/>
+      <c r="J100" s="29"/>
+    </row>
+    <row r="101" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="C101" s="39" t="s">
+      <c r="C101" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="D101" s="5" t="s">
+      <c r="D101" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E101" s="4" t="s">
@@ -3838,53 +3992,56 @@
       <c r="F101" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G101" s="16" t="s">
+      <c r="G101" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H101" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I101" s="19"/>
-    </row>
-    <row r="102" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="11"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="40"/>
-      <c r="D102" s="6"/>
+      <c r="H101" s="27"/>
+      <c r="I101" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J101" s="27"/>
+    </row>
+    <row r="102" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="34"/>
+      <c r="B102" s="37"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="37"/>
       <c r="E102" s="4" t="s">
         <v>231</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G102" s="17"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
-    </row>
-    <row r="103" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A103" s="12"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="41"/>
-      <c r="D103" s="7"/>
+      <c r="G102" s="41"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="28"/>
+      <c r="J102" s="28"/>
+    </row>
+    <row r="103" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A103" s="35"/>
+      <c r="B103" s="37"/>
+      <c r="C103" s="52"/>
+      <c r="D103" s="38"/>
       <c r="E103" s="4" t="s">
         <v>230</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="G103" s="18"/>
-      <c r="H103" s="21"/>
-      <c r="I103" s="21"/>
-    </row>
-    <row r="104" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="10" t="s">
+      <c r="G103" s="40"/>
+      <c r="H103" s="29"/>
+      <c r="I103" s="29"/>
+      <c r="J103" s="29"/>
+    </row>
+    <row r="104" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A104" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B104" s="6"/>
-      <c r="C104" s="39" t="s">
+      <c r="B104" s="37"/>
+      <c r="C104" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="D104" s="5" t="s">
+      <c r="D104" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E104" s="4" t="s">
@@ -3893,53 +4050,56 @@
       <c r="F104" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G104" s="16" t="s">
+      <c r="G104" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H104" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I104" s="19"/>
-    </row>
-    <row r="105" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="11"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="40"/>
-      <c r="D105" s="6"/>
+      <c r="H104" s="27"/>
+      <c r="I104" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J104" s="27"/>
+    </row>
+    <row r="105" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="34"/>
+      <c r="B105" s="37"/>
+      <c r="C105" s="57"/>
+      <c r="D105" s="37"/>
       <c r="E105" s="4" t="s">
         <v>231</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G105" s="17"/>
-      <c r="H105" s="20"/>
-      <c r="I105" s="20"/>
-    </row>
-    <row r="106" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A106" s="12"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="41"/>
-      <c r="D106" s="7"/>
+      <c r="G105" s="41"/>
+      <c r="H105" s="28"/>
+      <c r="I105" s="28"/>
+      <c r="J105" s="28"/>
+    </row>
+    <row r="106" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A106" s="35"/>
+      <c r="B106" s="37"/>
+      <c r="C106" s="52"/>
+      <c r="D106" s="38"/>
       <c r="E106" s="4" t="s">
         <v>234</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="G106" s="18"/>
-      <c r="H106" s="21"/>
-      <c r="I106" s="21"/>
-    </row>
-    <row r="107" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="10" t="s">
+      <c r="G106" s="40"/>
+      <c r="H106" s="29"/>
+      <c r="I106" s="29"/>
+      <c r="J106" s="29"/>
+    </row>
+    <row r="107" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A107" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B107" s="6"/>
-      <c r="C107" s="39" t="s">
+      <c r="B107" s="37"/>
+      <c r="C107" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="D107" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E107" s="3" t="s">
@@ -3948,128 +4108,136 @@
       <c r="F107" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G107" s="16" t="s">
+      <c r="G107" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H107" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I107" s="19"/>
-    </row>
-    <row r="108" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="11"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="40"/>
-      <c r="D108" s="6"/>
+      <c r="H107" s="27"/>
+      <c r="I107" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J107" s="27"/>
+    </row>
+    <row r="108" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="34"/>
+      <c r="B108" s="37"/>
+      <c r="C108" s="57"/>
+      <c r="D108" s="37"/>
       <c r="E108" s="3" t="s">
         <v>268</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G108" s="17"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
-    </row>
-    <row r="109" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="11"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="40"/>
-      <c r="D109" s="6"/>
+      <c r="G108" s="41"/>
+      <c r="H108" s="28"/>
+      <c r="I108" s="28"/>
+      <c r="J108" s="28"/>
+    </row>
+    <row r="109" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A109" s="34"/>
+      <c r="B109" s="37"/>
+      <c r="C109" s="57"/>
+      <c r="D109" s="37"/>
       <c r="E109" s="3" t="s">
         <v>236</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G109" s="17"/>
-      <c r="H109" s="20"/>
-      <c r="I109" s="20"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="11"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="40"/>
-      <c r="D110" s="6"/>
+      <c r="G109" s="41"/>
+      <c r="H109" s="28"/>
+      <c r="I109" s="28"/>
+      <c r="J109" s="28"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="34"/>
+      <c r="B110" s="37"/>
+      <c r="C110" s="57"/>
+      <c r="D110" s="37"/>
       <c r="E110" s="3" t="s">
         <v>245</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G110" s="17"/>
-      <c r="H110" s="20"/>
-      <c r="I110" s="20"/>
-    </row>
-    <row r="111" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A111" s="11"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="40"/>
-      <c r="D111" s="6"/>
+      <c r="G110" s="41"/>
+      <c r="H110" s="28"/>
+      <c r="I110" s="28"/>
+      <c r="J110" s="28"/>
+    </row>
+    <row r="111" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A111" s="34"/>
+      <c r="B111" s="37"/>
+      <c r="C111" s="57"/>
+      <c r="D111" s="37"/>
       <c r="E111" s="4" t="s">
         <v>235</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G111" s="17"/>
-      <c r="H111" s="20"/>
-      <c r="I111" s="20"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="11"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="40"/>
-      <c r="D112" s="6"/>
+      <c r="G111" s="41"/>
+      <c r="H111" s="28"/>
+      <c r="I111" s="28"/>
+      <c r="J111" s="28"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="34"/>
+      <c r="B112" s="37"/>
+      <c r="C112" s="57"/>
+      <c r="D112" s="37"/>
       <c r="E112" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G112" s="17"/>
-      <c r="H112" s="20"/>
-      <c r="I112" s="20"/>
-    </row>
-    <row r="113" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A113" s="11"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="40"/>
-      <c r="D113" s="6"/>
+      <c r="G112" s="41"/>
+      <c r="H112" s="28"/>
+      <c r="I112" s="28"/>
+      <c r="J112" s="28"/>
+    </row>
+    <row r="113" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A113" s="34"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="57"/>
+      <c r="D113" s="37"/>
       <c r="E113" s="4" t="s">
         <v>238</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G113" s="17"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="20"/>
-    </row>
-    <row r="114" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="12"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="41"/>
-      <c r="D114" s="7"/>
+      <c r="G113" s="41"/>
+      <c r="H113" s="28"/>
+      <c r="I113" s="28"/>
+      <c r="J113" s="28"/>
+    </row>
+    <row r="114" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="35"/>
+      <c r="B114" s="37"/>
+      <c r="C114" s="52"/>
+      <c r="D114" s="38"/>
       <c r="E114" s="4" t="s">
         <v>239</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="G114" s="18"/>
-      <c r="H114" s="21"/>
-      <c r="I114" s="21"/>
-    </row>
-    <row r="115" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A115" s="10" t="s">
+      <c r="G114" s="40"/>
+      <c r="H114" s="29"/>
+      <c r="I114" s="29"/>
+      <c r="J114" s="29"/>
+    </row>
+    <row r="115" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B115" s="6"/>
-      <c r="C115" s="55" t="s">
+      <c r="B115" s="37"/>
+      <c r="C115" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="D115" s="5" t="s">
+      <c r="D115" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E115" s="4" t="s">
@@ -4078,83 +4246,90 @@
       <c r="F115" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G115" s="16" t="s">
+      <c r="G115" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H115" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I115" s="19"/>
-    </row>
-    <row r="116" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="11"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="56"/>
-      <c r="D116" s="6"/>
+      <c r="H115" s="27"/>
+      <c r="I115" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J115" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A116" s="34"/>
+      <c r="B116" s="37"/>
+      <c r="C116" s="55"/>
+      <c r="D116" s="37"/>
       <c r="E116" s="3" t="s">
         <v>246</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G116" s="17"/>
-      <c r="H116" s="20"/>
-      <c r="I116" s="20"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="11"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="56"/>
-      <c r="D117" s="6"/>
+      <c r="G116" s="41"/>
+      <c r="H116" s="28"/>
+      <c r="I116" s="28"/>
+      <c r="J116" s="28"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="34"/>
+      <c r="B117" s="37"/>
+      <c r="C117" s="55"/>
+      <c r="D117" s="37"/>
       <c r="E117" s="3" t="s">
         <v>248</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G117" s="17"/>
-      <c r="H117" s="20"/>
-      <c r="I117" s="20"/>
-    </row>
-    <row r="118" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A118" s="11"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="56"/>
-      <c r="D118" s="6"/>
+      <c r="G117" s="41"/>
+      <c r="H117" s="28"/>
+      <c r="I117" s="28"/>
+      <c r="J117" s="28"/>
+    </row>
+    <row r="118" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A118" s="34"/>
+      <c r="B118" s="37"/>
+      <c r="C118" s="55"/>
+      <c r="D118" s="37"/>
       <c r="E118" s="4" t="s">
         <v>249</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G118" s="17"/>
-      <c r="H118" s="20"/>
-      <c r="I118" s="20"/>
-    </row>
-    <row r="119" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="12"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="57"/>
-      <c r="D119" s="7"/>
+      <c r="G118" s="41"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="28"/>
+      <c r="J118" s="28"/>
+    </row>
+    <row r="119" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A119" s="35"/>
+      <c r="B119" s="37"/>
+      <c r="C119" s="56"/>
+      <c r="D119" s="38"/>
       <c r="E119" s="4" t="s">
         <v>239</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G119" s="18"/>
-      <c r="H119" s="21"/>
-      <c r="I119" s="21"/>
-    </row>
-    <row r="120" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A120" s="10" t="s">
+      <c r="G119" s="40"/>
+      <c r="H119" s="29"/>
+      <c r="I119" s="29"/>
+      <c r="J119" s="29"/>
+    </row>
+    <row r="120" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A120" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="B120" s="6"/>
-      <c r="C120" s="55" t="s">
+      <c r="B120" s="37"/>
+      <c r="C120" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="D120" s="5" t="s">
+      <c r="D120" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E120" s="4" t="s">
@@ -4163,83 +4338,90 @@
       <c r="F120" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G120" s="16" t="s">
+      <c r="G120" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H120" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I120" s="19"/>
-    </row>
-    <row r="121" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="11"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="56"/>
-      <c r="D121" s="6"/>
+      <c r="H120" s="27"/>
+      <c r="I120" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J120" s="30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A121" s="34"/>
+      <c r="B121" s="37"/>
+      <c r="C121" s="55"/>
+      <c r="D121" s="37"/>
       <c r="E121" s="3" t="s">
         <v>246</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G121" s="17"/>
-      <c r="H121" s="20"/>
-      <c r="I121" s="20"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="11"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="56"/>
-      <c r="D122" s="6"/>
+      <c r="G121" s="41"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="28"/>
+      <c r="J121" s="31"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="34"/>
+      <c r="B122" s="37"/>
+      <c r="C122" s="55"/>
+      <c r="D122" s="37"/>
       <c r="E122" s="3" t="s">
         <v>247</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G122" s="17"/>
-      <c r="H122" s="20"/>
-      <c r="I122" s="20"/>
-    </row>
-    <row r="123" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A123" s="11"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="56"/>
-      <c r="D123" s="6"/>
+      <c r="G122" s="41"/>
+      <c r="H122" s="28"/>
+      <c r="I122" s="28"/>
+      <c r="J122" s="31"/>
+    </row>
+    <row r="123" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A123" s="34"/>
+      <c r="B123" s="37"/>
+      <c r="C123" s="55"/>
+      <c r="D123" s="37"/>
       <c r="E123" s="4" t="s">
         <v>249</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G123" s="17"/>
-      <c r="H123" s="20"/>
-      <c r="I123" s="20"/>
-    </row>
-    <row r="124" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="12"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="57"/>
-      <c r="D124" s="7"/>
+      <c r="G123" s="41"/>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28"/>
+      <c r="J123" s="31"/>
+    </row>
+    <row r="124" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="35"/>
+      <c r="B124" s="37"/>
+      <c r="C124" s="56"/>
+      <c r="D124" s="38"/>
       <c r="E124" s="4" t="s">
         <v>259</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G124" s="18"/>
-      <c r="H124" s="21"/>
-      <c r="I124" s="21"/>
-    </row>
-    <row r="125" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="10" t="s">
+      <c r="G124" s="40"/>
+      <c r="H124" s="29"/>
+      <c r="I124" s="29"/>
+      <c r="J124" s="32"/>
+    </row>
+    <row r="125" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="B125" s="6"/>
-      <c r="C125" s="39" t="s">
+      <c r="B125" s="37"/>
+      <c r="C125" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="D125" s="5" t="s">
+      <c r="D125" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E125" s="3" t="s">
@@ -4248,68 +4430,72 @@
       <c r="F125" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G125" s="16" t="s">
+      <c r="G125" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H125" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I125" s="19"/>
-    </row>
-    <row r="126" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="11"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="40"/>
-      <c r="D126" s="6"/>
+      <c r="H125" s="27"/>
+      <c r="I125" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J125" s="27"/>
+    </row>
+    <row r="126" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="34"/>
+      <c r="B126" s="37"/>
+      <c r="C126" s="57"/>
+      <c r="D126" s="37"/>
       <c r="E126" s="3" t="s">
         <v>246</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G126" s="17"/>
-      <c r="H126" s="20"/>
-      <c r="I126" s="20"/>
-    </row>
-    <row r="127" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="11"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="40"/>
-      <c r="D127" s="6"/>
+      <c r="G126" s="41"/>
+      <c r="H126" s="28"/>
+      <c r="I126" s="28"/>
+      <c r="J126" s="28"/>
+    </row>
+    <row r="127" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="34"/>
+      <c r="B127" s="37"/>
+      <c r="C127" s="57"/>
+      <c r="D127" s="37"/>
       <c r="E127" s="3" t="s">
         <v>255</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G127" s="17"/>
-      <c r="H127" s="20"/>
-      <c r="I127" s="20"/>
-    </row>
-    <row r="128" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A128" s="12"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="41"/>
-      <c r="D128" s="7"/>
+      <c r="G127" s="41"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="28"/>
+      <c r="J127" s="28"/>
+    </row>
+    <row r="128" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="35"/>
+      <c r="B128" s="37"/>
+      <c r="C128" s="52"/>
+      <c r="D128" s="38"/>
       <c r="E128" s="4" t="s">
         <v>252</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G128" s="18"/>
-      <c r="H128" s="21"/>
-      <c r="I128" s="21"/>
-    </row>
-    <row r="129" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="10" t="s">
+      <c r="G128" s="40"/>
+      <c r="H128" s="29"/>
+      <c r="I128" s="29"/>
+      <c r="J128" s="29"/>
+    </row>
+    <row r="129" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="B129" s="6"/>
-      <c r="C129" s="39" t="s">
+      <c r="B129" s="37"/>
+      <c r="C129" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="D129" s="5" t="s">
+      <c r="D129" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E129" s="3" t="s">
@@ -4318,113 +4504,120 @@
       <c r="F129" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G129" s="16" t="s">
+      <c r="G129" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H129" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I129" s="19"/>
-    </row>
-    <row r="130" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="11"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="40"/>
-      <c r="D130" s="6"/>
+      <c r="H129" s="27"/>
+      <c r="I129" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J129" s="27"/>
+    </row>
+    <row r="130" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="34"/>
+      <c r="B130" s="37"/>
+      <c r="C130" s="57"/>
+      <c r="D130" s="37"/>
       <c r="E130" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G130" s="17"/>
-      <c r="H130" s="20"/>
-      <c r="I130" s="20"/>
-    </row>
-    <row r="131" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="11"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="40"/>
-      <c r="D131" s="6"/>
+      <c r="G130" s="41"/>
+      <c r="H130" s="28"/>
+      <c r="I130" s="28"/>
+      <c r="J130" s="28"/>
+    </row>
+    <row r="131" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="34"/>
+      <c r="B131" s="37"/>
+      <c r="C131" s="57"/>
+      <c r="D131" s="37"/>
       <c r="E131" s="3" t="s">
         <v>256</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G131" s="17"/>
-      <c r="H131" s="20"/>
-      <c r="I131" s="20"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="11"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="40"/>
-      <c r="D132" s="6"/>
+      <c r="G131" s="41"/>
+      <c r="H131" s="28"/>
+      <c r="I131" s="28"/>
+      <c r="J131" s="28"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="34"/>
+      <c r="B132" s="37"/>
+      <c r="C132" s="57"/>
+      <c r="D132" s="37"/>
       <c r="E132" s="4" t="s">
         <v>258</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="G132" s="17"/>
-      <c r="H132" s="20"/>
-      <c r="I132" s="20"/>
-    </row>
-    <row r="133" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="11"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="40"/>
-      <c r="D133" s="6"/>
+      <c r="G132" s="41"/>
+      <c r="H132" s="28"/>
+      <c r="I132" s="28"/>
+      <c r="J132" s="28"/>
+    </row>
+    <row r="133" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A133" s="34"/>
+      <c r="B133" s="37"/>
+      <c r="C133" s="57"/>
+      <c r="D133" s="37"/>
       <c r="E133" s="3" t="s">
         <v>260</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G133" s="17"/>
-      <c r="H133" s="20"/>
-      <c r="I133" s="20"/>
-    </row>
-    <row r="134" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="11"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="40"/>
-      <c r="D134" s="6"/>
+      <c r="G133" s="41"/>
+      <c r="H133" s="28"/>
+      <c r="I133" s="28"/>
+      <c r="J133" s="28"/>
+    </row>
+    <row r="134" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="34"/>
+      <c r="B134" s="37"/>
+      <c r="C134" s="57"/>
+      <c r="D134" s="37"/>
       <c r="E134" s="3" t="s">
         <v>262</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G134" s="17"/>
-      <c r="H134" s="20"/>
-      <c r="I134" s="20"/>
-    </row>
-    <row r="135" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A135" s="12"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="41"/>
-      <c r="D135" s="7"/>
+      <c r="G134" s="41"/>
+      <c r="H134" s="28"/>
+      <c r="I134" s="28"/>
+      <c r="J134" s="28"/>
+    </row>
+    <row r="135" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A135" s="35"/>
+      <c r="B135" s="37"/>
+      <c r="C135" s="52"/>
+      <c r="D135" s="38"/>
       <c r="E135" s="4" t="s">
         <v>261</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G135" s="18"/>
-      <c r="H135" s="21"/>
-      <c r="I135" s="21"/>
-    </row>
-    <row r="136" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A136" s="10" t="s">
+      <c r="G135" s="40"/>
+      <c r="H135" s="29"/>
+      <c r="I135" s="29"/>
+      <c r="J135" s="29"/>
+    </row>
+    <row r="136" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A136" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B136" s="6"/>
-      <c r="C136" s="39" t="s">
+      <c r="B136" s="37"/>
+      <c r="C136" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="D136" s="5" t="s">
+      <c r="D136" s="36" t="s">
         <v>206</v>
       </c>
       <c r="E136" s="4" t="s">
@@ -4433,53 +4626,56 @@
       <c r="F136" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G136" s="16" t="s">
+      <c r="G136" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H136" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I136" s="19"/>
-    </row>
-    <row r="137" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="11"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="40"/>
-      <c r="D137" s="6"/>
+      <c r="H136" s="27"/>
+      <c r="I136" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J136" s="27"/>
+    </row>
+    <row r="137" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A137" s="34"/>
+      <c r="B137" s="37"/>
+      <c r="C137" s="57"/>
+      <c r="D137" s="37"/>
       <c r="E137" s="3" t="s">
         <v>246</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G137" s="17"/>
-      <c r="H137" s="20"/>
-      <c r="I137" s="20"/>
-    </row>
-    <row r="138" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A138" s="12"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="41"/>
-      <c r="D138" s="7"/>
+      <c r="G137" s="41"/>
+      <c r="H137" s="28"/>
+      <c r="I137" s="28"/>
+      <c r="J137" s="28"/>
+    </row>
+    <row r="138" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A138" s="35"/>
+      <c r="B138" s="37"/>
+      <c r="C138" s="52"/>
+      <c r="D138" s="38"/>
       <c r="E138" s="4" t="s">
         <v>266</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="G138" s="18"/>
-      <c r="H138" s="21"/>
-      <c r="I138" s="21"/>
-    </row>
-    <row r="139" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="10" t="s">
+      <c r="G138" s="40"/>
+      <c r="H138" s="29"/>
+      <c r="I138" s="29"/>
+      <c r="J138" s="29"/>
+    </row>
+    <row r="139" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A139" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B139" s="6"/>
-      <c r="C139" s="39" t="s">
+      <c r="B139" s="37"/>
+      <c r="C139" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="D139" s="5" t="s">
+      <c r="D139" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E139" s="3" t="s">
@@ -4488,98 +4684,104 @@
       <c r="F139" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G139" s="16" t="s">
+      <c r="G139" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H139" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I139" s="19"/>
-    </row>
-    <row r="140" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="11"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="40"/>
-      <c r="D140" s="6"/>
+      <c r="H139" s="27"/>
+      <c r="I139" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J139" s="27"/>
+    </row>
+    <row r="140" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A140" s="34"/>
+      <c r="B140" s="37"/>
+      <c r="C140" s="57"/>
+      <c r="D140" s="37"/>
       <c r="E140" s="4" t="s">
         <v>270</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G140" s="17"/>
-      <c r="H140" s="20"/>
-      <c r="I140" s="20"/>
-    </row>
-    <row r="141" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="11"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="40"/>
-      <c r="D141" s="6"/>
+      <c r="G140" s="41"/>
+      <c r="H140" s="28"/>
+      <c r="I140" s="28"/>
+      <c r="J140" s="28"/>
+    </row>
+    <row r="141" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="34"/>
+      <c r="B141" s="37"/>
+      <c r="C141" s="57"/>
+      <c r="D141" s="37"/>
       <c r="E141" s="3" t="s">
         <v>271</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G141" s="17"/>
-      <c r="H141" s="20"/>
-      <c r="I141" s="20"/>
-    </row>
-    <row r="142" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="11"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="40"/>
-      <c r="D142" s="6"/>
+      <c r="G141" s="41"/>
+      <c r="H141" s="28"/>
+      <c r="I141" s="28"/>
+      <c r="J141" s="28"/>
+    </row>
+    <row r="142" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A142" s="34"/>
+      <c r="B142" s="37"/>
+      <c r="C142" s="57"/>
+      <c r="D142" s="37"/>
       <c r="E142" s="3" t="s">
         <v>273</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G142" s="17"/>
-      <c r="H142" s="20"/>
-      <c r="I142" s="20"/>
-    </row>
-    <row r="143" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="11"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="40"/>
-      <c r="D143" s="6"/>
+      <c r="G142" s="41"/>
+      <c r="H142" s="28"/>
+      <c r="I142" s="28"/>
+      <c r="J142" s="28"/>
+    </row>
+    <row r="143" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A143" s="34"/>
+      <c r="B143" s="37"/>
+      <c r="C143" s="57"/>
+      <c r="D143" s="37"/>
       <c r="E143" s="3" t="s">
         <v>274</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G143" s="17"/>
-      <c r="H143" s="20"/>
-      <c r="I143" s="20"/>
-    </row>
-    <row r="144" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="12"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="41"/>
-      <c r="D144" s="7"/>
+      <c r="G143" s="41"/>
+      <c r="H143" s="28"/>
+      <c r="I143" s="28"/>
+      <c r="J143" s="28"/>
+    </row>
+    <row r="144" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="35"/>
+      <c r="B144" s="37"/>
+      <c r="C144" s="52"/>
+      <c r="D144" s="38"/>
       <c r="E144" s="3" t="s">
         <v>275</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G144" s="18"/>
-      <c r="H144" s="21"/>
-      <c r="I144" s="21"/>
-    </row>
-    <row r="145" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="10" t="s">
+      <c r="G144" s="40"/>
+      <c r="H144" s="29"/>
+      <c r="I144" s="29"/>
+      <c r="J144" s="29"/>
+    </row>
+    <row r="145" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A145" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B145" s="6"/>
-      <c r="C145" s="39" t="s">
+      <c r="B145" s="37"/>
+      <c r="C145" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="D145" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E145" s="3" t="s">
@@ -4588,83 +4790,88 @@
       <c r="F145" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G145" s="16" t="s">
+      <c r="G145" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H145" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I145" s="19"/>
-    </row>
-    <row r="146" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="11"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="40"/>
-      <c r="D146" s="6"/>
+      <c r="H145" s="27"/>
+      <c r="I145" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J145" s="27"/>
+    </row>
+    <row r="146" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A146" s="34"/>
+      <c r="B146" s="37"/>
+      <c r="C146" s="57"/>
+      <c r="D146" s="37"/>
       <c r="E146" s="4" t="s">
         <v>270</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G146" s="17"/>
-      <c r="H146" s="20"/>
-      <c r="I146" s="20"/>
-    </row>
-    <row r="147" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="11"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="40"/>
-      <c r="D147" s="6"/>
+      <c r="G146" s="41"/>
+      <c r="H146" s="28"/>
+      <c r="I146" s="28"/>
+      <c r="J146" s="28"/>
+    </row>
+    <row r="147" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="34"/>
+      <c r="B147" s="37"/>
+      <c r="C147" s="57"/>
+      <c r="D147" s="37"/>
       <c r="E147" s="3" t="s">
         <v>271</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G147" s="17"/>
-      <c r="H147" s="20"/>
-      <c r="I147" s="20"/>
-    </row>
-    <row r="148" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="11"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="40"/>
-      <c r="D148" s="6"/>
+      <c r="G147" s="41"/>
+      <c r="H147" s="28"/>
+      <c r="I147" s="28"/>
+      <c r="J147" s="28"/>
+    </row>
+    <row r="148" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A148" s="34"/>
+      <c r="B148" s="37"/>
+      <c r="C148" s="57"/>
+      <c r="D148" s="37"/>
       <c r="E148" s="3" t="s">
         <v>273</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G148" s="17"/>
-      <c r="H148" s="20"/>
-      <c r="I148" s="20"/>
-    </row>
-    <row r="149" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="12"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="41"/>
-      <c r="D149" s="7"/>
+      <c r="G148" s="41"/>
+      <c r="H148" s="28"/>
+      <c r="I148" s="28"/>
+      <c r="J148" s="28"/>
+    </row>
+    <row r="149" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A149" s="35"/>
+      <c r="B149" s="37"/>
+      <c r="C149" s="52"/>
+      <c r="D149" s="38"/>
       <c r="E149" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G149" s="18"/>
-      <c r="H149" s="21"/>
-      <c r="I149" s="21"/>
-    </row>
-    <row r="150" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="10" t="s">
+      <c r="G149" s="40"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="29"/>
+      <c r="J149" s="29"/>
+    </row>
+    <row r="150" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B150" s="6"/>
-      <c r="C150" s="39" t="s">
+      <c r="B150" s="37"/>
+      <c r="C150" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="D150" s="5" t="s">
+      <c r="D150" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E150" s="3" t="s">
@@ -4673,128 +4880,136 @@
       <c r="F150" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G150" s="16" t="s">
+      <c r="G150" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H150" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I150" s="19"/>
-    </row>
-    <row r="151" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A151" s="11"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="40"/>
-      <c r="D151" s="6"/>
+      <c r="H150" s="27"/>
+      <c r="I150" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J150" s="27"/>
+    </row>
+    <row r="151" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A151" s="34"/>
+      <c r="B151" s="37"/>
+      <c r="C151" s="57"/>
+      <c r="D151" s="37"/>
       <c r="E151" s="4" t="s">
         <v>270</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G151" s="17"/>
-      <c r="H151" s="20"/>
-      <c r="I151" s="20"/>
-    </row>
-    <row r="152" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="11"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="40"/>
-      <c r="D152" s="6"/>
+      <c r="G151" s="41"/>
+      <c r="H151" s="28"/>
+      <c r="I151" s="28"/>
+      <c r="J151" s="28"/>
+    </row>
+    <row r="152" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A152" s="34"/>
+      <c r="B152" s="37"/>
+      <c r="C152" s="57"/>
+      <c r="D152" s="37"/>
       <c r="E152" s="3" t="s">
         <v>271</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G152" s="17"/>
-      <c r="H152" s="20"/>
-      <c r="I152" s="20"/>
-    </row>
-    <row r="153" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="11"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="40"/>
-      <c r="D153" s="6"/>
+      <c r="G152" s="41"/>
+      <c r="H152" s="28"/>
+      <c r="I152" s="28"/>
+      <c r="J152" s="28"/>
+    </row>
+    <row r="153" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="34"/>
+      <c r="B153" s="37"/>
+      <c r="C153" s="57"/>
+      <c r="D153" s="37"/>
       <c r="E153" s="3" t="s">
         <v>273</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G153" s="17"/>
-      <c r="H153" s="20"/>
-      <c r="I153" s="20"/>
-    </row>
-    <row r="154" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="11"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="40"/>
-      <c r="D154" s="6"/>
+      <c r="G153" s="41"/>
+      <c r="H153" s="28"/>
+      <c r="I153" s="28"/>
+      <c r="J153" s="28"/>
+    </row>
+    <row r="154" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A154" s="34"/>
+      <c r="B154" s="37"/>
+      <c r="C154" s="57"/>
+      <c r="D154" s="37"/>
       <c r="E154" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G154" s="17"/>
-      <c r="H154" s="20"/>
-      <c r="I154" s="20"/>
-    </row>
-    <row r="155" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="11"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="40"/>
-      <c r="D155" s="6"/>
+      <c r="G154" s="41"/>
+      <c r="H154" s="28"/>
+      <c r="I154" s="28"/>
+      <c r="J154" s="28"/>
+    </row>
+    <row r="155" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A155" s="34"/>
+      <c r="B155" s="37"/>
+      <c r="C155" s="57"/>
+      <c r="D155" s="37"/>
       <c r="E155" s="3" t="s">
         <v>262</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G155" s="17"/>
-      <c r="H155" s="20"/>
-      <c r="I155" s="20"/>
-    </row>
-    <row r="156" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A156" s="11"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="40"/>
-      <c r="D156" s="6"/>
+      <c r="G155" s="41"/>
+      <c r="H155" s="28"/>
+      <c r="I155" s="28"/>
+      <c r="J155" s="28"/>
+    </row>
+    <row r="156" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A156" s="34"/>
+      <c r="B156" s="37"/>
+      <c r="C156" s="57"/>
+      <c r="D156" s="37"/>
       <c r="E156" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="G156" s="17"/>
-      <c r="H156" s="20"/>
-      <c r="I156" s="20"/>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="12"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="41"/>
-      <c r="D157" s="7"/>
+      <c r="G156" s="41"/>
+      <c r="H156" s="28"/>
+      <c r="I156" s="28"/>
+      <c r="J156" s="28"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="35"/>
+      <c r="B157" s="37"/>
+      <c r="C157" s="52"/>
+      <c r="D157" s="38"/>
       <c r="E157" s="4" t="s">
         <v>281</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="G157" s="18"/>
-      <c r="H157" s="21"/>
-      <c r="I157" s="21"/>
-    </row>
-    <row r="158" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="10" t="s">
+      <c r="G157" s="40"/>
+      <c r="H157" s="29"/>
+      <c r="I157" s="29"/>
+      <c r="J157" s="29"/>
+    </row>
+    <row r="158" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A158" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="B158" s="6"/>
-      <c r="C158" s="39" t="s">
+      <c r="B158" s="37"/>
+      <c r="C158" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="D158" s="5" t="s">
+      <c r="D158" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E158" s="3" t="s">
@@ -4803,55 +5018,58 @@
       <c r="F158" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G158" s="16" t="s">
+      <c r="G158" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H158" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I158" s="19"/>
-    </row>
-    <row r="159" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="11"/>
-      <c r="B159" s="6"/>
-      <c r="C159" s="40"/>
-      <c r="D159" s="6"/>
+      <c r="H158" s="27"/>
+      <c r="I158" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J158" s="27"/>
+    </row>
+    <row r="159" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A159" s="34"/>
+      <c r="B159" s="37"/>
+      <c r="C159" s="57"/>
+      <c r="D159" s="37"/>
       <c r="E159" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G159" s="17"/>
-      <c r="H159" s="20"/>
-      <c r="I159" s="20"/>
-    </row>
-    <row r="160" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A160" s="12"/>
-      <c r="B160" s="7"/>
-      <c r="C160" s="41"/>
-      <c r="D160" s="7"/>
+      <c r="G159" s="41"/>
+      <c r="H159" s="28"/>
+      <c r="I159" s="28"/>
+      <c r="J159" s="28"/>
+    </row>
+    <row r="160" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A160" s="35"/>
+      <c r="B160" s="38"/>
+      <c r="C160" s="52"/>
+      <c r="D160" s="38"/>
       <c r="E160" s="3" t="s">
         <v>284</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G160" s="18"/>
-      <c r="H160" s="21"/>
-      <c r="I160" s="21"/>
-    </row>
-    <row r="161" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="10" t="s">
+      <c r="G160" s="40"/>
+      <c r="H160" s="29"/>
+      <c r="I160" s="29"/>
+      <c r="J160" s="29"/>
+    </row>
+    <row r="161" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A161" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="B161" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C161" s="39" t="s">
+      <c r="C161" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="D161" s="5" t="s">
+      <c r="D161" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E161" s="3" t="s">
@@ -4860,68 +5078,74 @@
       <c r="F161" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G161" s="16" t="s">
+      <c r="G161" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H161" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I161" s="19"/>
-    </row>
-    <row r="162" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A162" s="11"/>
-      <c r="B162" s="6"/>
-      <c r="C162" s="40"/>
-      <c r="D162" s="6"/>
+      <c r="H161" s="27"/>
+      <c r="I161" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J161" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="34"/>
+      <c r="B162" s="37"/>
+      <c r="C162" s="57"/>
+      <c r="D162" s="37"/>
       <c r="E162" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G162" s="17"/>
-      <c r="H162" s="20"/>
-      <c r="I162" s="20"/>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="11"/>
-      <c r="B163" s="6"/>
-      <c r="C163" s="40"/>
-      <c r="D163" s="6"/>
+      <c r="G162" s="41"/>
+      <c r="H162" s="28"/>
+      <c r="I162" s="28"/>
+      <c r="J162" s="28"/>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="34"/>
+      <c r="B163" s="37"/>
+      <c r="C163" s="57"/>
+      <c r="D163" s="37"/>
       <c r="E163" s="4" t="s">
         <v>297</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G163" s="17"/>
-      <c r="H163" s="20"/>
-      <c r="I163" s="20"/>
-    </row>
-    <row r="164" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A164" s="12"/>
-      <c r="B164" s="6"/>
-      <c r="C164" s="41"/>
-      <c r="D164" s="7"/>
+      <c r="G163" s="41"/>
+      <c r="H163" s="28"/>
+      <c r="I163" s="28"/>
+      <c r="J163" s="28"/>
+    </row>
+    <row r="164" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A164" s="35"/>
+      <c r="B164" s="37"/>
+      <c r="C164" s="52"/>
+      <c r="D164" s="38"/>
       <c r="E164" s="3" t="s">
         <v>258</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="G164" s="18"/>
-      <c r="H164" s="21"/>
-      <c r="I164" s="21"/>
-    </row>
-    <row r="165" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A165" s="10" t="s">
+      <c r="G164" s="40"/>
+      <c r="H164" s="29"/>
+      <c r="I164" s="29"/>
+      <c r="J164" s="29"/>
+    </row>
+    <row r="165" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B165" s="6"/>
-      <c r="C165" s="39" t="s">
+      <c r="B165" s="37"/>
+      <c r="C165" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="D165" s="5" t="s">
+      <c r="D165" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E165" s="3" t="s">
@@ -4930,83 +5154,90 @@
       <c r="F165" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G165" s="16" t="s">
+      <c r="G165" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H165" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I165" s="19"/>
-    </row>
-    <row r="166" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="11"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="40"/>
-      <c r="D166" s="6"/>
+      <c r="H165" s="27"/>
+      <c r="I165" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J165" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A166" s="34"/>
+      <c r="B166" s="37"/>
+      <c r="C166" s="57"/>
+      <c r="D166" s="37"/>
       <c r="E166" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G166" s="17"/>
-      <c r="H166" s="20"/>
-      <c r="I166" s="20"/>
-    </row>
-    <row r="167" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="11"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="40"/>
-      <c r="D167" s="6"/>
+      <c r="G166" s="41"/>
+      <c r="H166" s="28"/>
+      <c r="I166" s="28"/>
+      <c r="J166" s="28"/>
+    </row>
+    <row r="167" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A167" s="34"/>
+      <c r="B167" s="37"/>
+      <c r="C167" s="57"/>
+      <c r="D167" s="37"/>
       <c r="E167" s="4" t="s">
         <v>304</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="G167" s="17"/>
-      <c r="H167" s="20"/>
-      <c r="I167" s="20"/>
-    </row>
-    <row r="168" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A168" s="11"/>
-      <c r="B168" s="6"/>
-      <c r="C168" s="40"/>
-      <c r="D168" s="6"/>
+      <c r="G167" s="41"/>
+      <c r="H167" s="28"/>
+      <c r="I167" s="28"/>
+      <c r="J167" s="28"/>
+    </row>
+    <row r="168" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="34"/>
+      <c r="B168" s="37"/>
+      <c r="C168" s="57"/>
+      <c r="D168" s="37"/>
       <c r="E168" s="3" t="s">
         <v>306</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="G168" s="17"/>
-      <c r="H168" s="20"/>
-      <c r="I168" s="20"/>
-    </row>
-    <row r="169" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A169" s="12"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="41"/>
-      <c r="D169" s="7"/>
+      <c r="G168" s="41"/>
+      <c r="H168" s="28"/>
+      <c r="I168" s="28"/>
+      <c r="J168" s="28"/>
+    </row>
+    <row r="169" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A169" s="35"/>
+      <c r="B169" s="37"/>
+      <c r="C169" s="52"/>
+      <c r="D169" s="38"/>
       <c r="E169" s="3" t="s">
         <v>289</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="G169" s="18"/>
-      <c r="H169" s="21"/>
-      <c r="I169" s="21"/>
-    </row>
-    <row r="170" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="10" t="s">
+      <c r="G169" s="40"/>
+      <c r="H169" s="29"/>
+      <c r="I169" s="29"/>
+      <c r="J169" s="29"/>
+    </row>
+    <row r="170" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A170" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B170" s="6"/>
-      <c r="C170" s="39" t="s">
+      <c r="B170" s="37"/>
+      <c r="C170" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="D170" s="5" t="s">
+      <c r="D170" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E170" s="3" t="s">
@@ -5015,113 +5246,120 @@
       <c r="F170" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G170" s="16" t="s">
+      <c r="G170" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H170" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I170" s="19"/>
-    </row>
-    <row r="171" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A171" s="11"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="40"/>
-      <c r="D171" s="6"/>
+      <c r="H170" s="27"/>
+      <c r="I170" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J170" s="27"/>
+    </row>
+    <row r="171" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="34"/>
+      <c r="B171" s="37"/>
+      <c r="C171" s="57"/>
+      <c r="D171" s="37"/>
       <c r="E171" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G171" s="17"/>
-      <c r="H171" s="20"/>
-      <c r="I171" s="20"/>
-    </row>
-    <row r="172" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A172" s="11"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="40"/>
-      <c r="D172" s="6"/>
+      <c r="G171" s="41"/>
+      <c r="H171" s="28"/>
+      <c r="I171" s="28"/>
+      <c r="J171" s="28"/>
+    </row>
+    <row r="172" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A172" s="34"/>
+      <c r="B172" s="37"/>
+      <c r="C172" s="57"/>
+      <c r="D172" s="37"/>
       <c r="E172" s="4" t="s">
         <v>216</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G172" s="17"/>
-      <c r="H172" s="20"/>
-      <c r="I172" s="20"/>
-    </row>
-    <row r="173" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="11"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="40"/>
-      <c r="D173" s="6"/>
+      <c r="G172" s="41"/>
+      <c r="H172" s="28"/>
+      <c r="I172" s="28"/>
+      <c r="J172" s="28"/>
+    </row>
+    <row r="173" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A173" s="34"/>
+      <c r="B173" s="37"/>
+      <c r="C173" s="57"/>
+      <c r="D173" s="37"/>
       <c r="E173" s="4" t="s">
         <v>310</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="G173" s="17"/>
-      <c r="H173" s="20"/>
-      <c r="I173" s="20"/>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="11"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="40"/>
-      <c r="D174" s="6"/>
+      <c r="G173" s="41"/>
+      <c r="H173" s="28"/>
+      <c r="I173" s="28"/>
+      <c r="J173" s="28"/>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="34"/>
+      <c r="B174" s="37"/>
+      <c r="C174" s="57"/>
+      <c r="D174" s="37"/>
       <c r="E174" s="4" t="s">
         <v>311</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="G174" s="17"/>
-      <c r="H174" s="20"/>
-      <c r="I174" s="20"/>
-    </row>
-    <row r="175" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A175" s="11"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="40"/>
-      <c r="D175" s="6"/>
+      <c r="G174" s="41"/>
+      <c r="H174" s="28"/>
+      <c r="I174" s="28"/>
+      <c r="J174" s="28"/>
+    </row>
+    <row r="175" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A175" s="34"/>
+      <c r="B175" s="37"/>
+      <c r="C175" s="57"/>
+      <c r="D175" s="37"/>
       <c r="E175" s="3" t="s">
         <v>313</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="G175" s="17"/>
-      <c r="H175" s="20"/>
-      <c r="I175" s="20"/>
-    </row>
-    <row r="176" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A176" s="12"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="41"/>
-      <c r="D176" s="7"/>
+      <c r="G175" s="41"/>
+      <c r="H175" s="28"/>
+      <c r="I175" s="28"/>
+      <c r="J175" s="28"/>
+    </row>
+    <row r="176" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A176" s="35"/>
+      <c r="B176" s="37"/>
+      <c r="C176" s="52"/>
+      <c r="D176" s="38"/>
       <c r="E176" s="3" t="s">
         <v>315</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="G176" s="18"/>
-      <c r="H176" s="21"/>
-      <c r="I176" s="21"/>
-    </row>
-    <row r="177" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A177" s="10" t="s">
+      <c r="G176" s="40"/>
+      <c r="H176" s="29"/>
+      <c r="I176" s="29"/>
+      <c r="J176" s="29"/>
+    </row>
+    <row r="177" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B177" s="6"/>
-      <c r="C177" s="39" t="s">
+      <c r="B177" s="37"/>
+      <c r="C177" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="D177" s="5" t="s">
+      <c r="D177" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E177" s="3" t="s">
@@ -5130,128 +5368,136 @@
       <c r="F177" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G177" s="16" t="s">
+      <c r="G177" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H177" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I177" s="19"/>
-    </row>
-    <row r="178" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A178" s="11"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="40"/>
-      <c r="D178" s="6"/>
+      <c r="H177" s="27"/>
+      <c r="I177" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J177" s="27"/>
+    </row>
+    <row r="178" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A178" s="34"/>
+      <c r="B178" s="37"/>
+      <c r="C178" s="57"/>
+      <c r="D178" s="37"/>
       <c r="E178" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G178" s="17"/>
-      <c r="H178" s="20"/>
-      <c r="I178" s="20"/>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="11"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="40"/>
-      <c r="D179" s="6"/>
+      <c r="G178" s="41"/>
+      <c r="H178" s="28"/>
+      <c r="I178" s="28"/>
+      <c r="J178" s="28"/>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="34"/>
+      <c r="B179" s="37"/>
+      <c r="C179" s="57"/>
+      <c r="D179" s="37"/>
       <c r="E179" s="4" t="s">
         <v>218</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G179" s="17"/>
-      <c r="H179" s="20"/>
-      <c r="I179" s="20"/>
-    </row>
-    <row r="180" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A180" s="11"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="40"/>
-      <c r="D180" s="6"/>
+      <c r="G179" s="41"/>
+      <c r="H179" s="28"/>
+      <c r="I179" s="28"/>
+      <c r="J179" s="28"/>
+    </row>
+    <row r="180" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A180" s="34"/>
+      <c r="B180" s="37"/>
+      <c r="C180" s="57"/>
+      <c r="D180" s="37"/>
       <c r="E180" s="4" t="s">
         <v>317</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="G180" s="17"/>
-      <c r="H180" s="20"/>
-      <c r="I180" s="20"/>
-    </row>
-    <row r="181" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A181" s="11"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="40"/>
-      <c r="D181" s="6"/>
+      <c r="G180" s="41"/>
+      <c r="H180" s="28"/>
+      <c r="I180" s="28"/>
+      <c r="J180" s="28"/>
+    </row>
+    <row r="181" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A181" s="34"/>
+      <c r="B181" s="37"/>
+      <c r="C181" s="57"/>
+      <c r="D181" s="37"/>
       <c r="E181" s="4" t="s">
         <v>319</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="G181" s="17"/>
-      <c r="H181" s="20"/>
-      <c r="I181" s="20"/>
-    </row>
-    <row r="182" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A182" s="11"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="40"/>
-      <c r="D182" s="6"/>
+      <c r="G181" s="41"/>
+      <c r="H181" s="28"/>
+      <c r="I181" s="28"/>
+      <c r="J181" s="28"/>
+    </row>
+    <row r="182" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A182" s="34"/>
+      <c r="B182" s="37"/>
+      <c r="C182" s="57"/>
+      <c r="D182" s="37"/>
       <c r="E182" s="3" t="s">
         <v>313</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="G182" s="17"/>
-      <c r="H182" s="20"/>
-      <c r="I182" s="20"/>
-    </row>
-    <row r="183" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A183" s="11"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="40"/>
-      <c r="D183" s="6"/>
+      <c r="G182" s="41"/>
+      <c r="H182" s="28"/>
+      <c r="I182" s="28"/>
+      <c r="J182" s="28"/>
+    </row>
+    <row r="183" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A183" s="34"/>
+      <c r="B183" s="37"/>
+      <c r="C183" s="57"/>
+      <c r="D183" s="37"/>
       <c r="E183" s="3" t="s">
         <v>315</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="G183" s="17"/>
-      <c r="H183" s="20"/>
-      <c r="I183" s="20"/>
-    </row>
-    <row r="184" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A184" s="12"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="41"/>
-      <c r="D184" s="7"/>
+      <c r="G183" s="41"/>
+      <c r="H183" s="28"/>
+      <c r="I183" s="28"/>
+      <c r="J183" s="28"/>
+    </row>
+    <row r="184" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A184" s="35"/>
+      <c r="B184" s="37"/>
+      <c r="C184" s="52"/>
+      <c r="D184" s="38"/>
       <c r="E184" s="3" t="s">
         <v>320</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G184" s="18"/>
-      <c r="H184" s="21"/>
-      <c r="I184" s="21"/>
-    </row>
-    <row r="185" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A185" s="10" t="s">
+      <c r="G184" s="40"/>
+      <c r="H184" s="29"/>
+      <c r="I184" s="29"/>
+      <c r="J184" s="29"/>
+    </row>
+    <row r="185" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A185" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B185" s="6"/>
-      <c r="C185" s="39" t="s">
+      <c r="B185" s="37"/>
+      <c r="C185" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="D185" s="5" t="s">
+      <c r="D185" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E185" s="3" t="s">
@@ -5260,68 +5506,72 @@
       <c r="F185" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G185" s="16" t="s">
+      <c r="G185" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H185" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I185" s="19"/>
-    </row>
-    <row r="186" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A186" s="11"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="40"/>
-      <c r="D186" s="6"/>
+      <c r="H185" s="27"/>
+      <c r="I185" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J185" s="27"/>
+    </row>
+    <row r="186" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="34"/>
+      <c r="B186" s="37"/>
+      <c r="C186" s="57"/>
+      <c r="D186" s="37"/>
       <c r="E186" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G186" s="17"/>
-      <c r="H186" s="20"/>
-      <c r="I186" s="20"/>
-    </row>
-    <row r="187" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A187" s="11"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="40"/>
-      <c r="D187" s="6"/>
+      <c r="G186" s="41"/>
+      <c r="H186" s="28"/>
+      <c r="I186" s="28"/>
+      <c r="J186" s="28"/>
+    </row>
+    <row r="187" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A187" s="34"/>
+      <c r="B187" s="37"/>
+      <c r="C187" s="57"/>
+      <c r="D187" s="37"/>
       <c r="E187" s="3" t="s">
         <v>294</v>
       </c>
       <c r="F187" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="G187" s="17"/>
-      <c r="H187" s="20"/>
-      <c r="I187" s="20"/>
-    </row>
-    <row r="188" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A188" s="12"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="41"/>
-      <c r="D188" s="7"/>
+      <c r="G187" s="41"/>
+      <c r="H187" s="28"/>
+      <c r="I187" s="28"/>
+      <c r="J187" s="28"/>
+    </row>
+    <row r="188" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A188" s="35"/>
+      <c r="B188" s="37"/>
+      <c r="C188" s="52"/>
+      <c r="D188" s="38"/>
       <c r="E188" s="3" t="s">
         <v>258</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="G188" s="18"/>
-      <c r="H188" s="21"/>
-      <c r="I188" s="21"/>
-    </row>
-    <row r="189" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A189" s="10" t="s">
+      <c r="G188" s="40"/>
+      <c r="H188" s="29"/>
+      <c r="I188" s="29"/>
+      <c r="J188" s="29"/>
+    </row>
+    <row r="189" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B189" s="6"/>
-      <c r="C189" s="39" t="s">
+      <c r="B189" s="37"/>
+      <c r="C189" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="D189" s="5" t="s">
+      <c r="D189" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E189" s="3" t="s">
@@ -5330,83 +5580,88 @@
       <c r="F189" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G189" s="16" t="s">
+      <c r="G189" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H189" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I189" s="19"/>
-    </row>
-    <row r="190" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="11"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="40"/>
-      <c r="D190" s="6"/>
+      <c r="H189" s="27"/>
+      <c r="I189" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J189" s="27"/>
+    </row>
+    <row r="190" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A190" s="34"/>
+      <c r="B190" s="37"/>
+      <c r="C190" s="57"/>
+      <c r="D190" s="37"/>
       <c r="E190" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G190" s="17"/>
-      <c r="H190" s="20"/>
-      <c r="I190" s="20"/>
-    </row>
-    <row r="191" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A191" s="11"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="40"/>
-      <c r="D191" s="6"/>
+      <c r="G190" s="41"/>
+      <c r="H190" s="28"/>
+      <c r="I190" s="28"/>
+      <c r="J190" s="28"/>
+    </row>
+    <row r="191" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A191" s="34"/>
+      <c r="B191" s="37"/>
+      <c r="C191" s="57"/>
+      <c r="D191" s="37"/>
       <c r="E191" s="3" t="s">
         <v>293</v>
       </c>
       <c r="F191" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="G191" s="17"/>
-      <c r="H191" s="20"/>
-      <c r="I191" s="20"/>
-    </row>
-    <row r="192" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A192" s="11"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="40"/>
-      <c r="D192" s="6"/>
+      <c r="G191" s="41"/>
+      <c r="H191" s="28"/>
+      <c r="I191" s="28"/>
+      <c r="J191" s="28"/>
+    </row>
+    <row r="192" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A192" s="34"/>
+      <c r="B192" s="37"/>
+      <c r="C192" s="57"/>
+      <c r="D192" s="37"/>
       <c r="E192" s="3" t="s">
         <v>296</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="G192" s="17"/>
-      <c r="H192" s="20"/>
-      <c r="I192" s="20"/>
-    </row>
-    <row r="193" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A193" s="12"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="41"/>
-      <c r="D193" s="7"/>
+      <c r="G192" s="41"/>
+      <c r="H192" s="28"/>
+      <c r="I192" s="28"/>
+      <c r="J192" s="28"/>
+    </row>
+    <row r="193" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A193" s="35"/>
+      <c r="B193" s="37"/>
+      <c r="C193" s="52"/>
+      <c r="D193" s="38"/>
       <c r="E193" s="3" t="s">
         <v>289</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="G193" s="18"/>
-      <c r="H193" s="21"/>
-      <c r="I193" s="21"/>
-    </row>
-    <row r="194" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A194" s="10" t="s">
+      <c r="G193" s="40"/>
+      <c r="H193" s="29"/>
+      <c r="I193" s="29"/>
+      <c r="J193" s="29"/>
+    </row>
+    <row r="194" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A194" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="B194" s="6"/>
-      <c r="C194" s="39" t="s">
+      <c r="B194" s="37"/>
+      <c r="C194" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D194" s="5" t="s">
+      <c r="D194" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E194" s="3" t="s">
@@ -5415,83 +5670,88 @@
       <c r="F194" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G194" s="16" t="s">
+      <c r="G194" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H194" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I194" s="19"/>
-    </row>
-    <row r="195" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A195" s="11"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="40"/>
-      <c r="D195" s="6"/>
+      <c r="H194" s="27"/>
+      <c r="I194" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J194" s="27"/>
+    </row>
+    <row r="195" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="34"/>
+      <c r="B195" s="37"/>
+      <c r="C195" s="57"/>
+      <c r="D195" s="37"/>
       <c r="E195" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G195" s="17"/>
-      <c r="H195" s="20"/>
-      <c r="I195" s="20"/>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="11"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="40"/>
-      <c r="D196" s="6"/>
+      <c r="G195" s="41"/>
+      <c r="H195" s="28"/>
+      <c r="I195" s="28"/>
+      <c r="J195" s="28"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="34"/>
+      <c r="B196" s="37"/>
+      <c r="C196" s="57"/>
+      <c r="D196" s="37"/>
       <c r="E196" s="4" t="s">
         <v>297</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G196" s="17"/>
-      <c r="H196" s="20"/>
-      <c r="I196" s="20"/>
-    </row>
-    <row r="197" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A197" s="11"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="40"/>
-      <c r="D197" s="6"/>
+      <c r="G196" s="41"/>
+      <c r="H196" s="28"/>
+      <c r="I196" s="28"/>
+      <c r="J196" s="28"/>
+    </row>
+    <row r="197" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A197" s="34"/>
+      <c r="B197" s="37"/>
+      <c r="C197" s="57"/>
+      <c r="D197" s="37"/>
       <c r="E197" s="3" t="s">
         <v>299</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="G197" s="17"/>
-      <c r="H197" s="20"/>
-      <c r="I197" s="20"/>
-    </row>
-    <row r="198" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A198" s="12"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="41"/>
-      <c r="D198" s="7"/>
+      <c r="G197" s="41"/>
+      <c r="H197" s="28"/>
+      <c r="I197" s="28"/>
+      <c r="J197" s="28"/>
+    </row>
+    <row r="198" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A198" s="35"/>
+      <c r="B198" s="37"/>
+      <c r="C198" s="52"/>
+      <c r="D198" s="38"/>
       <c r="E198" s="4" t="s">
         <v>235</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G198" s="18"/>
-      <c r="H198" s="21"/>
-      <c r="I198" s="21"/>
-    </row>
-    <row r="199" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A199" s="10" t="s">
+      <c r="G198" s="40"/>
+      <c r="H198" s="29"/>
+      <c r="I198" s="29"/>
+      <c r="J198" s="29"/>
+    </row>
+    <row r="199" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A199" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B199" s="6"/>
-      <c r="C199" s="39" t="s">
+      <c r="B199" s="37"/>
+      <c r="C199" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="D199" s="5" t="s">
+      <c r="D199" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E199" s="3" t="s">
@@ -5500,83 +5760,88 @@
       <c r="F199" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G199" s="16" t="s">
+      <c r="G199" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H199" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I199" s="19"/>
-    </row>
-    <row r="200" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A200" s="11"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="40"/>
-      <c r="D200" s="6"/>
+      <c r="H199" s="27"/>
+      <c r="I199" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J199" s="27"/>
+    </row>
+    <row r="200" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A200" s="34"/>
+      <c r="B200" s="37"/>
+      <c r="C200" s="57"/>
+      <c r="D200" s="37"/>
       <c r="E200" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G200" s="17"/>
-      <c r="H200" s="20"/>
-      <c r="I200" s="20"/>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="11"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="40"/>
-      <c r="D201" s="6"/>
+      <c r="G200" s="41"/>
+      <c r="H200" s="28"/>
+      <c r="I200" s="28"/>
+      <c r="J200" s="28"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="34"/>
+      <c r="B201" s="37"/>
+      <c r="C201" s="57"/>
+      <c r="D201" s="37"/>
       <c r="E201" s="4" t="s">
         <v>297</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G201" s="17"/>
-      <c r="H201" s="20"/>
-      <c r="I201" s="20"/>
-    </row>
-    <row r="202" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A202" s="11"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="40"/>
-      <c r="D202" s="6"/>
+      <c r="G201" s="41"/>
+      <c r="H201" s="28"/>
+      <c r="I201" s="28"/>
+      <c r="J201" s="28"/>
+    </row>
+    <row r="202" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A202" s="34"/>
+      <c r="B202" s="37"/>
+      <c r="C202" s="57"/>
+      <c r="D202" s="37"/>
       <c r="E202" s="3" t="s">
         <v>299</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="G202" s="17"/>
-      <c r="H202" s="20"/>
-      <c r="I202" s="20"/>
-    </row>
-    <row r="203" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A203" s="11"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="40"/>
-      <c r="D203" s="6"/>
+      <c r="G202" s="41"/>
+      <c r="H202" s="28"/>
+      <c r="I202" s="28"/>
+      <c r="J202" s="28"/>
+    </row>
+    <row r="203" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A203" s="34"/>
+      <c r="B203" s="37"/>
+      <c r="C203" s="57"/>
+      <c r="D203" s="37"/>
       <c r="E203" s="3" t="s">
         <v>350</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="G203" s="17"/>
-      <c r="H203" s="20"/>
-      <c r="I203" s="20"/>
-    </row>
-    <row r="204" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A204" s="10" t="s">
+      <c r="G203" s="41"/>
+      <c r="H203" s="28"/>
+      <c r="I203" s="28"/>
+      <c r="J203" s="28"/>
+    </row>
+    <row r="204" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A204" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="B204" s="6"/>
-      <c r="C204" s="39" t="s">
+      <c r="B204" s="37"/>
+      <c r="C204" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="D204" s="5" t="s">
+      <c r="D204" s="36" t="s">
         <v>227</v>
       </c>
       <c r="E204" s="3" t="s">
@@ -5585,55 +5850,60 @@
       <c r="F204" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G204" s="16" t="s">
+      <c r="G204" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H204" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I204" s="19"/>
-    </row>
-    <row r="205" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="11"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="40"/>
-      <c r="D205" s="6"/>
+      <c r="H204" s="27"/>
+      <c r="I204" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J204" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A205" s="34"/>
+      <c r="B205" s="37"/>
+      <c r="C205" s="57"/>
+      <c r="D205" s="37"/>
       <c r="E205" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G205" s="17"/>
-      <c r="H205" s="20"/>
-      <c r="I205" s="20"/>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="12"/>
-      <c r="B206" s="7"/>
-      <c r="C206" s="41"/>
-      <c r="D206" s="7"/>
+      <c r="G205" s="41"/>
+      <c r="H205" s="28"/>
+      <c r="I205" s="28"/>
+      <c r="J205" s="28"/>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="35"/>
+      <c r="B206" s="38"/>
+      <c r="C206" s="52"/>
+      <c r="D206" s="38"/>
       <c r="E206" s="3" t="s">
         <v>288</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="G206" s="18"/>
-      <c r="H206" s="21"/>
-      <c r="I206" s="21"/>
-    </row>
-    <row r="207" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="10" t="s">
+      <c r="G206" s="40"/>
+      <c r="H206" s="29"/>
+      <c r="I206" s="29"/>
+      <c r="J206" s="29"/>
+    </row>
+    <row r="207" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B207" s="5" t="s">
+      <c r="B207" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C207" s="39" t="s">
+      <c r="C207" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="D207" s="5" t="s">
+      <c r="D207" s="36" t="s">
         <v>330</v>
       </c>
       <c r="E207" s="4" t="s">
@@ -5642,35 +5912,37 @@
       <c r="F207" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G207" s="16" t="s">
+      <c r="G207" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="H207" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I207" s="19"/>
-    </row>
-    <row r="208" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A208" s="12"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="41"/>
-      <c r="D208" s="7"/>
+      <c r="H207" s="27"/>
+      <c r="I207" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J207" s="27"/>
+    </row>
+    <row r="208" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A208" s="35"/>
+      <c r="B208" s="37"/>
+      <c r="C208" s="52"/>
+      <c r="D208" s="38"/>
       <c r="E208" s="4" t="s">
         <v>327</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G208" s="18"/>
-      <c r="H208" s="20"/>
-      <c r="I208" s="20"/>
-    </row>
-    <row r="209" spans="1:9" ht="51" x14ac:dyDescent="0.25">
+      <c r="G208" s="40"/>
+      <c r="H208" s="28"/>
+      <c r="I208" s="28"/>
+      <c r="J208" s="28"/>
+    </row>
+    <row r="209" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B209" s="7"/>
-      <c r="C209" s="42" t="s">
+      <c r="B209" s="38"/>
+      <c r="C209" s="20" t="s">
         <v>121</v>
       </c>
       <c r="D209" s="4" t="s">
@@ -5682,22 +5954,23 @@
       <c r="F209" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="G209" s="32" t="s">
+      <c r="G209" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="H209" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="I209" s="33"/>
-    </row>
-    <row r="210" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="H209" s="17"/>
+      <c r="I209" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="J209" s="17"/>
+    </row>
+    <row r="210" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B210" s="5" t="s">
+      <c r="B210" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="C210" s="42" t="s">
+      <c r="C210" s="20" t="s">
         <v>122</v>
       </c>
       <c r="D210" s="4" t="s">
@@ -5709,22 +5982,23 @@
       <c r="F210" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="G210" s="32" t="s">
+      <c r="G210" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H210" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="I210" s="31" t="s">
+      <c r="H210" s="15" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="I210" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="J210" s="15"/>
+    </row>
+    <row r="211" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B211" s="6"/>
-      <c r="C211" s="42" t="s">
+      <c r="B211" s="37"/>
+      <c r="C211" s="20" t="s">
         <v>123</v>
       </c>
       <c r="D211" s="4" t="s">
@@ -5736,122 +6010,127 @@
       <c r="F211" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="G211" s="9" t="s">
+      <c r="G211" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H211" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="I211" s="31" t="s">
+      <c r="H211" s="15" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A212" s="15" t="s">
+      <c r="I211" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="J211" s="15"/>
+    </row>
+    <row r="212" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A212" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B212" s="6"/>
-      <c r="C212" s="43" t="s">
+      <c r="B212" s="37"/>
+      <c r="C212" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="D212" s="13" t="s">
+      <c r="D212" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="E212" s="13" t="s">
+      <c r="E212" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="F212" s="15" t="s">
+      <c r="F212" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="G212" s="29" t="s">
+      <c r="G212" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H212" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="I212" s="30"/>
-    </row>
-    <row r="213" spans="1:9" ht="102" x14ac:dyDescent="0.25">
-      <c r="A213" s="26" t="s">
+      <c r="H212" s="14"/>
+      <c r="I212" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J212" s="14"/>
+    </row>
+    <row r="213" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+      <c r="A213" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B213" s="35" t="s">
+      <c r="B213" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="C213" s="38" t="s">
+      <c r="C213" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D213" s="26" t="s">
+      <c r="D213" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E213" s="26" t="s">
+      <c r="E213" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="F213" s="26" t="s">
+      <c r="F213" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="G213" s="34" t="s">
+      <c r="G213" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H213" s="33" t="s">
-        <v>359</v>
-      </c>
-      <c r="I213" s="33" t="s">
+      <c r="H213" s="17" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="214" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A214" s="26" t="s">
+      <c r="I213" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="J213" s="17"/>
+    </row>
+    <row r="214" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A214" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B214" s="36"/>
-      <c r="C214" s="38" t="s">
+      <c r="B214" s="59"/>
+      <c r="C214" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="D214" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E214" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="F214" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="G214" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H214" s="11"/>
+      <c r="I214" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="J214" s="17"/>
+    </row>
+    <row r="215" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A215" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B215" s="60"/>
+      <c r="C215" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="D214" s="26" t="s">
+      <c r="D215" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E214" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="F214" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="G214" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H214" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="I214" s="26"/>
-    </row>
-    <row r="215" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A215" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B215" s="37"/>
-      <c r="C215" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D215" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="E215" s="26" t="s">
+      <c r="E215" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="F215" s="26" t="s">
+      <c r="F215" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="G215" s="34" t="s">
+      <c r="G215" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H215" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="I215" s="26"/>
+      <c r="H215" s="11"/>
+      <c r="I215" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="J215" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="273">
+  <mergeCells count="317">
     <mergeCell ref="I199:I203"/>
     <mergeCell ref="I204:I206"/>
     <mergeCell ref="I207:I208"/>
@@ -5908,6 +6187,18 @@
     <mergeCell ref="A177:A184"/>
     <mergeCell ref="G177:G184"/>
     <mergeCell ref="H177:H184"/>
+    <mergeCell ref="C185:C188"/>
+    <mergeCell ref="D185:D188"/>
+    <mergeCell ref="G185:G188"/>
+    <mergeCell ref="H185:H188"/>
+    <mergeCell ref="H189:H193"/>
+    <mergeCell ref="G189:G193"/>
+    <mergeCell ref="D204:D206"/>
+    <mergeCell ref="C204:C206"/>
+    <mergeCell ref="B161:B206"/>
+    <mergeCell ref="G204:G206"/>
+    <mergeCell ref="H204:H206"/>
+    <mergeCell ref="A204:A206"/>
     <mergeCell ref="A161:A164"/>
     <mergeCell ref="G161:G164"/>
     <mergeCell ref="H161:H164"/>
@@ -5932,18 +6223,6 @@
     <mergeCell ref="A194:A198"/>
     <mergeCell ref="G194:G198"/>
     <mergeCell ref="G199:G203"/>
-    <mergeCell ref="C185:C188"/>
-    <mergeCell ref="D185:D188"/>
-    <mergeCell ref="G185:G188"/>
-    <mergeCell ref="H185:H188"/>
-    <mergeCell ref="H189:H193"/>
-    <mergeCell ref="G189:G193"/>
-    <mergeCell ref="D204:D206"/>
-    <mergeCell ref="C204:C206"/>
-    <mergeCell ref="B161:B206"/>
-    <mergeCell ref="G204:G206"/>
-    <mergeCell ref="H204:H206"/>
-    <mergeCell ref="A204:A206"/>
     <mergeCell ref="D189:D193"/>
     <mergeCell ref="C189:C193"/>
     <mergeCell ref="A189:A193"/>
@@ -6125,6 +6404,50 @@
     <mergeCell ref="B2:B14"/>
     <mergeCell ref="B210:B212"/>
     <mergeCell ref="B207:B209"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J41:J51"/>
+    <mergeCell ref="J52:J63"/>
+    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="J67:J76"/>
+    <mergeCell ref="J77:J84"/>
+    <mergeCell ref="J85:J88"/>
+    <mergeCell ref="J89:J92"/>
+    <mergeCell ref="J93:J100"/>
+    <mergeCell ref="J101:J103"/>
+    <mergeCell ref="J104:J106"/>
+    <mergeCell ref="J107:J114"/>
+    <mergeCell ref="J115:J119"/>
+    <mergeCell ref="J120:J124"/>
+    <mergeCell ref="J125:J128"/>
+    <mergeCell ref="J177:J184"/>
+    <mergeCell ref="J185:J188"/>
+    <mergeCell ref="J189:J193"/>
+    <mergeCell ref="J194:J198"/>
+    <mergeCell ref="J199:J203"/>
+    <mergeCell ref="J204:J206"/>
+    <mergeCell ref="J207:J208"/>
+    <mergeCell ref="J129:J135"/>
+    <mergeCell ref="J136:J138"/>
+    <mergeCell ref="J139:J144"/>
+    <mergeCell ref="J145:J149"/>
+    <mergeCell ref="J150:J157"/>
+    <mergeCell ref="J158:J160"/>
+    <mergeCell ref="J161:J164"/>
+    <mergeCell ref="J165:J169"/>
+    <mergeCell ref="J170:J176"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
